--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E525"/>
+  <dimension ref="A1:E531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11457,6 +11457,132 @@
         <v>349.46</v>
       </c>
       <c r="E525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="C526" t="n">
+        <v>308.26</v>
+      </c>
+      <c r="D526" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>328.49</v>
+      </c>
+      <c r="C527" t="n">
+        <v>308.94</v>
+      </c>
+      <c r="D527" t="n">
+        <v>350.32</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="C528" t="n">
+        <v>308.67</v>
+      </c>
+      <c r="D528" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>331.53</v>
+      </c>
+      <c r="C529" t="n">
+        <v>308.57</v>
+      </c>
+      <c r="D529" t="n">
+        <v>351.66</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="C530" t="n">
+        <v>308.38</v>
+      </c>
+      <c r="D530" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>334.31</v>
+      </c>
+      <c r="C531" t="n">
+        <v>307.83</v>
+      </c>
+      <c r="D531" t="n">
+        <v>349.75</v>
+      </c>
+      <c r="E531" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11473,7 +11599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17666,6 +17792,66 @@
       </c>
       <c r="B619" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -17834,28 +18020,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.16840484765917</v>
+        <v>0.1729038603110507</v>
       </c>
       <c r="J2" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="K2" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03009939664936767</v>
+        <v>0.03231291380117296</v>
       </c>
       <c r="M2" t="n">
-        <v>6.095784049563808</v>
+        <v>6.054861304561374</v>
       </c>
       <c r="N2" t="n">
-        <v>56.87723816444667</v>
+        <v>56.35878539803043</v>
       </c>
       <c r="O2" t="n">
-        <v>7.541699951897229</v>
+        <v>7.507248856807029</v>
       </c>
       <c r="P2" t="n">
-        <v>324.1021906235138</v>
+        <v>324.0563194254065</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17912,28 +18098,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1247154890463228</v>
+        <v>0.1036915775708438</v>
       </c>
       <c r="J3" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="K3" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02193954284496613</v>
+        <v>0.01519099464264928</v>
       </c>
       <c r="M3" t="n">
-        <v>5.369503889654623</v>
+        <v>5.431090415746657</v>
       </c>
       <c r="N3" t="n">
-        <v>43.1557628387782</v>
+        <v>43.8779356539038</v>
       </c>
       <c r="O3" t="n">
-        <v>6.569304593241069</v>
+        <v>6.624042244272284</v>
       </c>
       <c r="P3" t="n">
-        <v>315.5933285457168</v>
+        <v>315.8073687037331</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17990,28 +18176,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4405737662051806</v>
+        <v>0.4334041589123362</v>
       </c>
       <c r="J4" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="K4" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1303781477389133</v>
+        <v>0.1290354959051689</v>
       </c>
       <c r="M4" t="n">
-        <v>7.165835751793292</v>
+        <v>7.130904441449326</v>
       </c>
       <c r="N4" t="n">
-        <v>80.57916964563127</v>
+        <v>79.8124848085745</v>
       </c>
       <c r="O4" t="n">
-        <v>8.976590090097201</v>
+        <v>8.933783342379336</v>
       </c>
       <c r="P4" t="n">
-        <v>342.4497296583549</v>
+        <v>342.5227208914104</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18049,7 +18235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E525"/>
+  <dimension ref="A1:E531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32227,6 +32413,168 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-34.966489557944925,173.65299869677176</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-34.96674884757746,173.65386695804446</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-34.96645667811326,173.65481128028802</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-34.966481583969845,173.65299979667236</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-34.96674275509924,173.6538677983792</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-34.96645802204314,173.65481109493092</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-34.96647029497138,173.65300135383464</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-34.96674517417147,173.65386746471688</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-34.96645381106288,173.65481167571645</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-34.96645434702111,173.65300355363465</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-34.96674607012417,173.65386734113824</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-34.96644601626963,173.65481275078739</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-34.96643553202351,173.6530061489033</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-34.96674777243425,173.6538671063388</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-34.96644780817613,173.65481250364468</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-34.96642943954808,173.65300698927578</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-34.966752700173984,173.65386642665624</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-34.96646312897662,173.6548103905739</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E531"/>
+  <dimension ref="A1:E536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>334.31</v>
+        <v>332.66</v>
       </c>
       <c r="C531" t="n">
         <v>307.83</v>
@@ -11583,6 +11583,111 @@
         <v>349.75</v>
       </c>
       <c r="E531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>331.92</v>
+      </c>
+      <c r="C532" t="n">
+        <v>307.63</v>
+      </c>
+      <c r="D532" t="n">
+        <v>347.57</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>331.77</v>
+      </c>
+      <c r="C533" t="n">
+        <v>308.03</v>
+      </c>
+      <c r="D533" t="n">
+        <v>347.79</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="C534" t="n">
+        <v>308.26</v>
+      </c>
+      <c r="D534" t="n">
+        <v>347.78</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="C535" t="n">
+        <v>308.22</v>
+      </c>
+      <c r="D535" t="n">
+        <v>347.31</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>336.01</v>
+      </c>
+      <c r="C536" t="n">
+        <v>308.49</v>
+      </c>
+      <c r="D536" t="n">
+        <v>346.86</v>
+      </c>
+      <c r="E536" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11599,7 +11704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17852,6 +17957,56 @@
       </c>
       <c r="B625" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -18020,28 +18175,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1729038603110507</v>
+        <v>0.1806843217754672</v>
       </c>
       <c r="J2" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="K2" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03231291380117296</v>
+        <v>0.03566883199567705</v>
       </c>
       <c r="M2" t="n">
-        <v>6.054861304561374</v>
+        <v>6.038913243314123</v>
       </c>
       <c r="N2" t="n">
-        <v>56.35878539803043</v>
+        <v>56.06667337911107</v>
       </c>
       <c r="O2" t="n">
-        <v>7.507248856807029</v>
+        <v>7.487768250894993</v>
       </c>
       <c r="P2" t="n">
-        <v>324.0563194254065</v>
+        <v>323.9767548520667</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18098,28 +18253,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1036915775708438</v>
+        <v>0.08657897621711093</v>
       </c>
       <c r="J3" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="K3" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01519099464264928</v>
+        <v>0.01059445933763259</v>
       </c>
       <c r="M3" t="n">
-        <v>5.431090415746657</v>
+        <v>5.479967624373811</v>
       </c>
       <c r="N3" t="n">
-        <v>43.8779356539038</v>
+        <v>44.46793531046303</v>
       </c>
       <c r="O3" t="n">
-        <v>6.624042244272284</v>
+        <v>6.668428248880168</v>
       </c>
       <c r="P3" t="n">
-        <v>315.8073687037331</v>
+        <v>315.9822635101452</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18176,28 +18331,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4334041589123362</v>
+        <v>0.4223389041607832</v>
       </c>
       <c r="J4" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="K4" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1290354959051689</v>
+        <v>0.1247632455179071</v>
       </c>
       <c r="M4" t="n">
-        <v>7.130904441449326</v>
+        <v>7.135194526715313</v>
       </c>
       <c r="N4" t="n">
-        <v>79.8124848085745</v>
+        <v>79.48544212343656</v>
       </c>
       <c r="O4" t="n">
-        <v>8.933783342379336</v>
+        <v>8.915460847507354</v>
       </c>
       <c r="P4" t="n">
-        <v>342.5227208914104</v>
+        <v>342.635820037822</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18235,7 +18390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E531"/>
+  <dimension ref="A1:E536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32556,7 +32711,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>-34.96642943954808,173.65300698927578</t>
+          <t>-34.96644422276052,173.6530049501365</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32570,6 +32725,141 @@
         </is>
       </c>
       <c r="E531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-34.96645085280728,173.6530040356132</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-34.966754492079346,173.6538661794989</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-34.966482660757286,173.65480769671655</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-34.96645219673567,173.65300385023684</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-34.96675090826864,173.65386667381355</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-34.96648068966016,173.65480796857378</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-34.96643078347648,173.6530068038995</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-34.96674884757746,173.65386695804446</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-34.966480779255484,173.65480795621662</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-34.96642101759672,173.65300815096694</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-34.96674920595854,173.65386690861297</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-34.96648499023571,173.65480737543072</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-34.966414208359446,173.6530090902064</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-34.966746786886304,173.65386724227534</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-34.96648902202528,173.65480681935907</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E536"/>
+  <dimension ref="A1:E539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11690,6 +11690,69 @@
       <c r="E536" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>336.79</v>
+      </c>
+      <c r="C537" t="n">
+        <v>307.51</v>
+      </c>
+      <c r="D537" t="n">
+        <v>348.24</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:17:33+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>335.78</v>
+      </c>
+      <c r="C538" t="n">
+        <v>307.39</v>
+      </c>
+      <c r="D538" t="n">
+        <v>348.01</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>335.78</v>
+      </c>
+      <c r="C539" t="n">
+        <v>307.74</v>
+      </c>
+      <c r="D539" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B630"/>
+  <dimension ref="A1:B634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18007,6 +18070,46 @@
       </c>
       <c r="B630" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -18175,28 +18278,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1806843217754672</v>
+        <v>0.1877117665122882</v>
       </c>
       <c r="J2" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K2" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03566883199567705</v>
+        <v>0.03860177693679945</v>
       </c>
       <c r="M2" t="n">
-        <v>6.038913243314123</v>
+        <v>6.042550725499496</v>
       </c>
       <c r="N2" t="n">
-        <v>56.06667337911107</v>
+        <v>56.04264012258298</v>
       </c>
       <c r="O2" t="n">
-        <v>7.487768250894993</v>
+        <v>7.486163244451926</v>
       </c>
       <c r="P2" t="n">
-        <v>323.9767548520667</v>
+        <v>323.9046117270738</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18253,28 +18356,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08657897621711093</v>
+        <v>0.07610824693091175</v>
       </c>
       <c r="J3" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K3" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01059445933763259</v>
+        <v>0.008178947624211896</v>
       </c>
       <c r="M3" t="n">
-        <v>5.479967624373811</v>
+        <v>5.510559198589879</v>
       </c>
       <c r="N3" t="n">
-        <v>44.46793531046303</v>
+        <v>44.85789674646847</v>
       </c>
       <c r="O3" t="n">
-        <v>6.668428248880168</v>
+        <v>6.697603806322711</v>
       </c>
       <c r="P3" t="n">
-        <v>315.9822635101452</v>
+        <v>316.0897583593436</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18331,28 +18434,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4223389041607832</v>
+        <v>0.4166596903602204</v>
       </c>
       <c r="J4" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K4" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1247632455179071</v>
+        <v>0.1227535940242652</v>
       </c>
       <c r="M4" t="n">
-        <v>7.135194526715313</v>
+        <v>7.131917790469069</v>
       </c>
       <c r="N4" t="n">
-        <v>79.48544212343656</v>
+        <v>79.23004986973469</v>
       </c>
       <c r="O4" t="n">
-        <v>8.915460847507354</v>
+        <v>8.901126325905878</v>
       </c>
       <c r="P4" t="n">
-        <v>342.635820037822</v>
+        <v>342.6941241269481</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18390,7 +18493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E536"/>
+  <dimension ref="A1:E539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32865,6 +32968,87 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-34.9664072199317,173.6530100541626</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-34.966755567222556,173.65386603120447</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-34.96647665787059,173.65480852464532</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:17:33+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-34.96641626904968,173.6530088059629</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-34.96675664236577,173.6538658829101</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-34.96647871856304,173.65480824043098</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-34.96641626904968,173.6530088059629</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-34.9667535065314,173.6538663154354</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-34.96647450758281,173.6548088212168</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
